--- a/data/trans_orig/P57_AF_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P57_AF_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo afectivo bajo (Duke) en 2007</t>
+          <t>Población con apoyo afectivo bajo (Duke) en 2007 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>256940</t>
+          <t>257151</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>299785</t>
+          <t>300422</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>145526</t>
+          <t>145745</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>180684</t>
+          <t>181140</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>413586</t>
+          <t>415273</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>469361</t>
+          <t>471572</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,64%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>171156</t>
+          <t>170519</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>214001</t>
+          <t>213790</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>125996</t>
+          <t>125540</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>161154</t>
+          <t>160935</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>308260</t>
+          <t>306049</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>364035</t>
+          <t>362348</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,6%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>178772</t>
+          <t>176973</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>214891</t>
+          <t>216651</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>202076</t>
+          <t>202392</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>239113</t>
+          <t>237872</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>390129</t>
+          <t>387908</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>443966</t>
+          <t>442461</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>59,89%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>152043</t>
+          <t>150283</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>188162</t>
+          <t>189961</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>132752</t>
+          <t>133993</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>169789</t>
+          <t>169473</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>294833</t>
+          <t>296338</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>348670</t>
+          <t>350891</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,49%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>331354</t>
+          <t>333194</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>377100</t>
+          <t>376475</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>94889</t>
+          <t>93733</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>118312</t>
+          <t>117978</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>436187</t>
+          <t>437916</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>486105</t>
+          <t>486150</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>164445</t>
+          <t>165070</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>210191</t>
+          <t>208351</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48490</t>
+          <t>48824</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71913</t>
+          <t>73069</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>222242</t>
+          <t>222197</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>272160</t>
+          <t>270431</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,18%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>753934</t>
+          <t>754995</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>824380</t>
+          <t>825552</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>441008</t>
+          <t>437494</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>490337</t>
+          <t>489493</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1212240</t>
+          <t>1216644</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1297371</t>
+          <t>1297770</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,46%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>413954</t>
+          <t>412782</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>484400</t>
+          <t>483339</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>223948</t>
+          <t>224792</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>273277</t>
+          <t>276791</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>655249</t>
+          <t>654850</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>740380</t>
+          <t>735976</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,69%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>201165</t>
+          <t>201950</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>236984</t>
+          <t>238221</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>354047</t>
+          <t>353898</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>400529</t>
+          <t>399538</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>564658</t>
+          <t>566125</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>626971</t>
+          <t>626246</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,2%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>113571</t>
+          <t>112334</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>149390</t>
+          <t>148605</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>167228</t>
+          <t>168219</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>213710</t>
+          <t>213859</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>291341</t>
+          <t>292066</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>353654</t>
+          <t>352187</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,35%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>125335</t>
+          <t>124933</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>157964</t>
+          <t>159994</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>696685</t>
+          <t>695342</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>765297</t>
+          <t>765338</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>835334</t>
+          <t>834776</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>915814</t>
+          <t>915559</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,22%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>139399</t>
+          <t>137369</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>172028</t>
+          <t>172430</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>483463</t>
+          <t>483422</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>552075</t>
+          <t>553418</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>630309</t>
+          <t>630564</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>710789</t>
+          <t>711347</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>46,01%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1921402</t>
+          <t>1925725</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2038030</t>
+          <t>2037241</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2011246</t>
+          <t>2013143</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2123935</t>
+          <t>2123655</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3968041</t>
+          <t>3970723</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4123320</t>
+          <t>4129172</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,17%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1227643</t>
+          <t>1228432</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1344271</t>
+          <t>1339948</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1252214</t>
+          <t>1252494</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1364903</t>
+          <t>1363006</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2518502</t>
+          <t>2512650</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2673781</t>
+          <t>2671099</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,22%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo afectivo bajo (Duke) en 2012</t>
+          <t>Población con apoyo afectivo bajo (Duke) en 2012 (tasa de respuesta: 99,34%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>232239</t>
+          <t>232180</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>274462</t>
+          <t>274155</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>171393</t>
+          <t>172043</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>208461</t>
+          <t>208374</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>417691</t>
+          <t>418291</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>475615</t>
+          <t>472809</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,25%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>160822</t>
+          <t>161129</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>203045</t>
+          <t>203104</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>103780</t>
+          <t>103867</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>140848</t>
+          <t>140198</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>271909</t>
+          <t>274715</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>329833</t>
+          <t>329233</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,04%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>231351</t>
+          <t>231650</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>273989</t>
+          <t>272461</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>201170</t>
+          <t>203226</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>239794</t>
+          <t>240195</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>449503</t>
+          <t>447311</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>502926</t>
+          <t>501567</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,74%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>142328</t>
+          <t>143856</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>184966</t>
+          <t>184667</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>95447</t>
+          <t>95046</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>134071</t>
+          <t>132015</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>248632</t>
+          <t>249991</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>302055</t>
+          <t>304247</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,48%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>359667</t>
+          <t>359416</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>409208</t>
+          <t>408169</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>151946</t>
+          <t>151440</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>182300</t>
+          <t>182551</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>523894</t>
+          <t>524775</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>582185</t>
+          <t>582688</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,71%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>218415</t>
+          <t>219454</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>267956</t>
+          <t>268207</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>76893</t>
+          <t>76642</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>107247</t>
+          <t>107753</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>304630</t>
+          <t>304127</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>362921</t>
+          <t>362040</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,82%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>705835</t>
+          <t>702047</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>770754</t>
+          <t>771802</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>510757</t>
+          <t>511748</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>564728</t>
+          <t>563943</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1233545</t>
+          <t>1239165</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1315823</t>
+          <t>1319265</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>69,0%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>378527</t>
+          <t>377479</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>443446</t>
+          <t>447234</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>197952</t>
+          <t>198737</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>251923</t>
+          <t>250932</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>596137</t>
+          <t>592695</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>678415</t>
+          <t>672795</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,19%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>319282</t>
+          <t>319004</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>360586</t>
+          <t>361681</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>506697</t>
+          <t>505585</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>555962</t>
+          <t>555287</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>838371</t>
+          <t>837453</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>905981</t>
+          <t>905646</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,89%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>144912</t>
+          <t>143817</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>186216</t>
+          <t>186494</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>198384</t>
+          <t>199059</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>247649</t>
+          <t>248761</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>353862</t>
+          <t>354197</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>421472</t>
+          <t>422390</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>121486</t>
+          <t>121556</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>153815</t>
+          <t>154217</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>666937</t>
+          <t>669499</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>731585</t>
+          <t>734808</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>801749</t>
+          <t>802460</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>875370</t>
+          <t>880998</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,45%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>113067</t>
+          <t>112665</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>145396</t>
+          <t>145326</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>368519</t>
+          <t>365296</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>433167</t>
+          <t>430605</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>491616</t>
+          <t>485988</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>565237</t>
+          <t>564526</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,3%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2049609</t>
+          <t>2049666</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2165423</t>
+          <t>2166906</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2297367</t>
+          <t>2296250</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2410219</t>
+          <t>2412891</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4381608</t>
+          <t>4375691</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4543612</t>
+          <t>4541168</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,58%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1235461</t>
+          <t>1233978</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1351275</t>
+          <t>1351218</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1113585</t>
+          <t>1110913</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1226437</t>
+          <t>1227554</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2381076</t>
+          <t>2383520</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2543080</t>
+          <t>2548997</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,81%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo afectivo bajo (Duke) en 2016</t>
+          <t>Población con apoyo afectivo bajo (Duke) en 2016 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>270981</t>
+          <t>269045</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>311501</t>
+          <t>312875</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>225894</t>
+          <t>225157</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>260325</t>
+          <t>259326</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>507456</t>
+          <t>508724</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>560405</t>
+          <t>560749</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,76%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>116726</t>
+          <t>115352</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>157246</t>
+          <t>159182</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>82163</t>
+          <t>83162</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>116594</t>
+          <t>117331</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>210310</t>
+          <t>209966</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>263259</t>
+          <t>261991</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,99%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>242595</t>
+          <t>242303</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>280087</t>
+          <t>280594</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>239560</t>
+          <t>241561</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>276494</t>
+          <t>276379</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>490934</t>
+          <t>493479</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>543522</t>
+          <t>545048</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,31%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>95743</t>
+          <t>95236</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>133235</t>
+          <t>133527</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>91146</t>
+          <t>91261</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>128080</t>
+          <t>126079</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>199948</t>
+          <t>198422</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>252536</t>
+          <t>249991</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,62%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>379160</t>
+          <t>379372</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>417999</t>
+          <t>417092</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>116497</t>
+          <t>116893</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>137629</t>
+          <t>137829</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>505700</t>
+          <t>502069</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>548626</t>
+          <t>549151</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>79,99%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>103915</t>
+          <t>104822</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>142754</t>
+          <t>142542</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26949</t>
+          <t>26749</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48081</t>
+          <t>47685</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>137866</t>
+          <t>137341</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>180792</t>
+          <t>184423</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,86%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>825533</t>
+          <t>827103</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>884592</t>
+          <t>885667</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>588489</t>
+          <t>593109</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>639294</t>
+          <t>641199</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1432118</t>
+          <t>1431941</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1513041</t>
+          <t>1509039</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>76,89%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>255117</t>
+          <t>254042</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>314176</t>
+          <t>312606</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>183663</t>
+          <t>181758</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>234468</t>
+          <t>229848</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>449625</t>
+          <t>453627</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>530548</t>
+          <t>530725</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,04%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>458510</t>
+          <t>458617</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>502110</t>
+          <t>501419</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>573925</t>
+          <t>575952</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>617876</t>
+          <t>616623</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1047025</t>
+          <t>1047497</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1103151</t>
+          <t>1107490</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,74%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>116412</t>
+          <t>117103</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>160012</t>
+          <t>159905</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>118559</t>
+          <t>119812</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>162510</t>
+          <t>160483</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>251807</t>
+          <t>247468</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>307933</t>
+          <t>307461</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,69%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>183872</t>
+          <t>183831</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>215703</t>
+          <t>213638</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>799879</t>
+          <t>799507</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>857065</t>
+          <t>854242</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>998220</t>
+          <t>996927</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1062185</t>
+          <t>1063644</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,92%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>70491</t>
+          <t>72556</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>102322</t>
+          <t>102363</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>221791</t>
+          <t>224614</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>278977</t>
+          <t>279349</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>302865</t>
+          <t>301406</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>366830</t>
+          <t>368123</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,97%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2436828</t>
+          <t>2440069</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2542200</t>
+          <t>2541315</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2615951</t>
+          <t>2624727</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2720701</t>
+          <t>2716016</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5080954</t>
+          <t>5086372</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5229606</t>
+          <t>5235407</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>76,06%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>828196</t>
+          <t>829081</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>933568</t>
+          <t>930327</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>792254</t>
+          <t>796939</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>897004</t>
+          <t>888228</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1653745</t>
+          <t>1647944</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1802397</t>
+          <t>1796979</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo afectivo bajo (Duke) en 2023</t>
+          <t>Población con apoyo afectivo bajo (Duke) en 2023 (tasa de respuesta: 98,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>233675</t>
+          <t>236620</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>279261</t>
+          <t>281270</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>184238</t>
+          <t>182668</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>221538</t>
+          <t>218491</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>428537</t>
+          <t>432574</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>487982</t>
+          <t>490989</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,81%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>222276</t>
+          <t>220267</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>267862</t>
+          <t>264917</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>224550</t>
+          <t>227597</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>261850</t>
+          <t>263420</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>459643</t>
+          <t>456636</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>519088</t>
+          <t>515051</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,35%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>228934</t>
+          <t>229203</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>273373</t>
+          <t>273005</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>194850</t>
+          <t>196901</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>229072</t>
+          <t>229292</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>437062</t>
+          <t>432148</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>491540</t>
+          <t>489382</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,19%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>175036</t>
+          <t>175404</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>219475</t>
+          <t>219206</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>149372</t>
+          <t>149152</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>183594</t>
+          <t>181543</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>335314</t>
+          <t>337472</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>389792</t>
+          <t>394706</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,74%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>84760</t>
+          <t>95780</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>394938</t>
+          <t>396762</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>84773</t>
+          <t>83613</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>105242</t>
+          <t>104615</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>138452</t>
+          <t>137392</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>487992</t>
+          <t>491599</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>59,23%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>269909</t>
+          <t>268085</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>580087</t>
+          <t>569067</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59923</t>
+          <t>60550</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>80392</t>
+          <t>81552</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>342020</t>
+          <t>338413</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>691560</t>
+          <t>692620</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,45%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>572695</t>
+          <t>569580</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>647152</t>
+          <t>644169</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>540071</t>
+          <t>539727</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>800186</t>
+          <t>799006</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1146915</t>
+          <t>1146312</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1479720</t>
+          <t>1514563</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>75,69%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>381395</t>
+          <t>384378</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>455852</t>
+          <t>458967</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>172333</t>
+          <t>173513</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>432448</t>
+          <t>432792</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>521346</t>
+          <t>486503</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>854151</t>
+          <t>854754</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,71%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>269501</t>
+          <t>270178</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>316180</t>
+          <t>317655</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>348438</t>
+          <t>369150</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>534053</t>
+          <t>534260</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>639121</t>
+          <t>619199</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>834831</t>
+          <t>833502</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,16%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>152557</t>
+          <t>151082</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>199236</t>
+          <t>198559</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>296295</t>
+          <t>296088</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>481910</t>
+          <t>461198</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>464254</t>
+          <t>465583</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>659964</t>
+          <t>679886</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>52,34%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>62970</t>
+          <t>61628</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>112644</t>
+          <t>108609</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>417812</t>
+          <t>420233</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>471515</t>
+          <t>472310</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>492704</t>
+          <t>494495</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>566471</t>
+          <t>567931</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,24%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>125223</t>
+          <t>129258</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>174897</t>
+          <t>176239</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>282841</t>
+          <t>282046</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>336544</t>
+          <t>334123</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>425752</t>
+          <t>424292</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>499519</t>
+          <t>497728</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,16%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1345864</t>
+          <t>1292323</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1897182</t>
+          <t>1898230</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1940549</t>
+          <t>1919948</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2329157</t>
+          <t>2320172</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3397061</t>
+          <t>3414697</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4064034</t>
+          <t>4081664</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>59,18%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1452762</t>
+          <t>1451714</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2004080</t>
+          <t>2057621</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1217764</t>
+          <t>1226749</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1606372</t>
+          <t>1626973</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2832831</t>
+          <t>2815201</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3499804</t>
+          <t>3482168</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,49%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57_AF_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P57_AF_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>257151</t>
+          <t>252642</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>300422</t>
+          <t>299427</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>145745</t>
+          <t>145467</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>181140</t>
+          <t>180401</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>415273</t>
+          <t>416083</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>471572</t>
+          <t>472167</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>60,72%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>170519</t>
+          <t>171514</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>213790</t>
+          <t>218299</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>125540</t>
+          <t>126279</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>160935</t>
+          <t>161213</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>306049</t>
+          <t>305454</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>362348</t>
+          <t>361538</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,49%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>176973</t>
+          <t>177697</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>216651</t>
+          <t>215311</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>202392</t>
+          <t>202466</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>237872</t>
+          <t>239030</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>387908</t>
+          <t>390101</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>442461</t>
+          <t>443499</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>60,03%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>150283</t>
+          <t>151623</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>189961</t>
+          <t>189237</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>133993</t>
+          <t>132835</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>169473</t>
+          <t>169399</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>296338</t>
+          <t>295300</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>350891</t>
+          <t>348698</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,2%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>333194</t>
+          <t>331663</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>376475</t>
+          <t>377999</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>93733</t>
+          <t>94391</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>117978</t>
+          <t>119040</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>437916</t>
+          <t>435663</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>486150</t>
+          <t>485553</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>68,55%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>165070</t>
+          <t>163546</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>208351</t>
+          <t>209882</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48824</t>
+          <t>47762</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73069</t>
+          <t>72411</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>222197</t>
+          <t>222794</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>270431</t>
+          <t>272684</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,5%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>754995</t>
+          <t>754881</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>825552</t>
+          <t>824534</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>437494</t>
+          <t>437908</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>489493</t>
+          <t>490596</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1216644</t>
+          <t>1213911</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1297770</t>
+          <t>1297157</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,43%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>412782</t>
+          <t>413800</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>483339</t>
+          <t>483453</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>224792</t>
+          <t>223689</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>276791</t>
+          <t>276377</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>654850</t>
+          <t>655463</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>735976</t>
+          <t>738709</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,83%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>201950</t>
+          <t>200093</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>238221</t>
+          <t>237227</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>353898</t>
+          <t>353883</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>399538</t>
+          <t>401324</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>566125</t>
+          <t>568383</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>626246</t>
+          <t>624631</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>68,02%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>112334</t>
+          <t>113328</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>148605</t>
+          <t>150462</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>168219</t>
+          <t>166433</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>213859</t>
+          <t>213874</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>292066</t>
+          <t>293681</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>352187</t>
+          <t>349929</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,11%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>124933</t>
+          <t>125105</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>159994</t>
+          <t>157379</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>695342</t>
+          <t>700228</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>765338</t>
+          <t>768024</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>834776</t>
+          <t>837549</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>915559</t>
+          <t>912919</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,05%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>137369</t>
+          <t>139984</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>172430</t>
+          <t>172258</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>483422</t>
+          <t>480736</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>553418</t>
+          <t>548532</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>630564</t>
+          <t>633204</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>711347</t>
+          <t>708574</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>45,83%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1925725</t>
+          <t>1921793</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2037241</t>
+          <t>2035721</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2013143</t>
+          <t>2010867</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2123655</t>
+          <t>2124756</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3970723</t>
+          <t>3971700</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4129172</t>
+          <t>4121907</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,06%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1228432</t>
+          <t>1229952</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1339948</t>
+          <t>1343880</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1252494</t>
+          <t>1251393</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1363006</t>
+          <t>1365282</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2512650</t>
+          <t>2519915</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2671099</t>
+          <t>2670122</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,2%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>232180</t>
+          <t>232189</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>274155</t>
+          <t>276799</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>172043</t>
+          <t>170498</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>208374</t>
+          <t>208470</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>418291</t>
+          <t>418078</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>472809</t>
+          <t>475877</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,66%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>161129</t>
+          <t>158485</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>203104</t>
+          <t>203095</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>103867</t>
+          <t>103771</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>140198</t>
+          <t>141743</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>274715</t>
+          <t>271647</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>329233</t>
+          <t>329446</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,07%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>231650</t>
+          <t>232440</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>272461</t>
+          <t>273658</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>203226</t>
+          <t>204155</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>240195</t>
+          <t>240891</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>447311</t>
+          <t>443544</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>501567</t>
+          <t>502531</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,87%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>143856</t>
+          <t>142659</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>184667</t>
+          <t>183877</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>95046</t>
+          <t>94350</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>132015</t>
+          <t>131086</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>249991</t>
+          <t>249027</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>304247</t>
+          <t>308014</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,98%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>359416</t>
+          <t>357864</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>408169</t>
+          <t>408136</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>151440</t>
+          <t>151912</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>182551</t>
+          <t>184364</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>524775</t>
+          <t>520827</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>582688</t>
+          <t>581148</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,53%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>219454</t>
+          <t>219487</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>268207</t>
+          <t>269759</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>76642</t>
+          <t>74829</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>107753</t>
+          <t>107281</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>304127</t>
+          <t>305667</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>362040</t>
+          <t>365988</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>41,27%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>702047</t>
+          <t>703024</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>771802</t>
+          <t>771107</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>511748</t>
+          <t>511706</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>563943</t>
+          <t>563311</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1239165</t>
+          <t>1234396</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1319265</t>
+          <t>1317103</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>68,89%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>377479</t>
+          <t>378174</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>447234</t>
+          <t>446257</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>198737</t>
+          <t>199369</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>250932</t>
+          <t>250974</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>592695</t>
+          <t>594857</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>672795</t>
+          <t>677564</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,44%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>319004</t>
+          <t>317216</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>361681</t>
+          <t>360845</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>505585</t>
+          <t>505572</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>555287</t>
+          <t>555506</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>837453</t>
+          <t>839694</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>905646</t>
+          <t>905632</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,88%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>143817</t>
+          <t>144653</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>186494</t>
+          <t>188282</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>199059</t>
+          <t>198840</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>248761</t>
+          <t>248774</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>354197</t>
+          <t>354211</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>422390</t>
+          <t>420149</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,35%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>121556</t>
+          <t>123469</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>154217</t>
+          <t>155670</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>669499</t>
+          <t>665096</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>734808</t>
+          <t>731951</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>802460</t>
+          <t>803286</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>880998</t>
+          <t>876782</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,14%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>112665</t>
+          <t>111212</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>145326</t>
+          <t>143413</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>365296</t>
+          <t>368153</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>430605</t>
+          <t>435008</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>485988</t>
+          <t>490204</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>564526</t>
+          <t>563700</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,24%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2049666</t>
+          <t>2050218</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2166906</t>
+          <t>2166945</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2296250</t>
+          <t>2299511</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2412891</t>
+          <t>2407066</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4375691</t>
+          <t>4381862</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4541168</t>
+          <t>4542912</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,6%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1233978</t>
+          <t>1233939</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1351218</t>
+          <t>1350666</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1110913</t>
+          <t>1116738</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1227554</t>
+          <t>1224293</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2383520</t>
+          <t>2381776</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2548997</t>
+          <t>2542826</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,72%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>269045</t>
+          <t>270565</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>312875</t>
+          <t>311947</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>225157</t>
+          <t>225041</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>259326</t>
+          <t>259196</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>508724</t>
+          <t>507299</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>560749</t>
+          <t>563743</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>73,15%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>115352</t>
+          <t>116280</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>159182</t>
+          <t>157662</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83162</t>
+          <t>83292</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>117331</t>
+          <t>117447</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>209966</t>
+          <t>206972</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>261991</t>
+          <t>263416</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,18%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>242303</t>
+          <t>243405</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>280594</t>
+          <t>279214</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>241561</t>
+          <t>238627</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>276379</t>
+          <t>275770</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>493479</t>
+          <t>494202</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>545048</t>
+          <t>545594</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,38%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>95236</t>
+          <t>96616</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>133527</t>
+          <t>132425</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>91261</t>
+          <t>91870</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>126079</t>
+          <t>129013</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>198422</t>
+          <t>197876</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>249991</t>
+          <t>249268</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>379372</t>
+          <t>378080</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>417092</t>
+          <t>417740</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>116893</t>
+          <t>116734</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>137829</t>
+          <t>138381</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>502069</t>
+          <t>502134</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>549151</t>
+          <t>546538</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,61%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>104822</t>
+          <t>104174</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>142542</t>
+          <t>143834</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26749</t>
+          <t>26197</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47685</t>
+          <t>47844</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>137341</t>
+          <t>139954</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>184423</t>
+          <t>184358</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>827103</t>
+          <t>830069</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>885667</t>
+          <t>888114</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>593109</t>
+          <t>590804</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>641199</t>
+          <t>640864</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1431941</t>
+          <t>1428197</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1509039</t>
+          <t>1511711</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>77,02%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>254042</t>
+          <t>251595</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>312606</t>
+          <t>309640</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>181758</t>
+          <t>182093</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>229848</t>
+          <t>232153</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>453627</t>
+          <t>450955</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>530725</t>
+          <t>534469</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,23%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>458617</t>
+          <t>459218</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>501419</t>
+          <t>500983</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>575952</t>
+          <t>572730</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>616623</t>
+          <t>618000</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1047497</t>
+          <t>1045457</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1107490</t>
+          <t>1108715</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,83%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>117103</t>
+          <t>117539</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>159905</t>
+          <t>159304</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>119812</t>
+          <t>118435</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>160483</t>
+          <t>163705</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>247468</t>
+          <t>246243</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>307461</t>
+          <t>309501</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,84%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>183831</t>
+          <t>185394</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>213638</t>
+          <t>216017</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>799507</t>
+          <t>803537</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>854242</t>
+          <t>855387</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>996927</t>
+          <t>996417</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1063644</t>
+          <t>1061479</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,76%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>72556</t>
+          <t>70177</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>102363</t>
+          <t>100800</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>224614</t>
+          <t>223469</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>279349</t>
+          <t>275319</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>301406</t>
+          <t>303571</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>368123</t>
+          <t>368633</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2440069</t>
+          <t>2446681</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2541315</t>
+          <t>2551547</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2624727</t>
+          <t>2616542</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2716016</t>
+          <t>2721594</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5086372</t>
+          <t>5086853</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5235407</t>
+          <t>5234604</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,05%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>829081</t>
+          <t>818849</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>930327</t>
+          <t>923715</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>796939</t>
+          <t>791361</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>888228</t>
+          <t>896413</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1647944</t>
+          <t>1648747</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1796979</t>
+          <t>1796498</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>257985</t>
+          <t>284315</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>236620</t>
+          <t>260525</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>281270</t>
+          <t>306015</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>200993</t>
+          <t>222914</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>182668</t>
+          <t>202778</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>218491</t>
+          <t>241016</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>458979</t>
+          <t>507230</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>432574</t>
+          <t>478702</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>490989</t>
+          <t>539548</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>52,18%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>243552</t>
+          <t>262572</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>220267</t>
+          <t>240872</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>264917</t>
+          <t>286362</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>245095</t>
+          <t>264114</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>227597</t>
+          <t>246012</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>263420</t>
+          <t>284250</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>488646</t>
+          <t>526685</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>456636</t>
+          <t>494367</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>515051</t>
+          <t>555213</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>53,7%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>501537</t>
+          <t>546887</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>501537</t>
+          <t>546887</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>501537</t>
+          <t>546887</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>446088</t>
+          <t>487028</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>446088</t>
+          <t>487028</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>446088</t>
+          <t>487028</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>947625</t>
+          <t>1033915</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>947625</t>
+          <t>1033915</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>947625</t>
+          <t>1033915</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>250650</t>
+          <t>276069</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>229203</t>
+          <t>253416</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>273005</t>
+          <t>298763</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>212807</t>
+          <t>234634</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>196901</t>
+          <t>216042</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>229292</t>
+          <t>251092</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>463458</t>
+          <t>510703</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>432148</t>
+          <t>481735</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>489382</t>
+          <t>540525</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>60,17%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>197759</t>
+          <t>203262</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>175404</t>
+          <t>180568</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>219206</t>
+          <t>225915</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>165637</t>
+          <t>184302</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>149152</t>
+          <t>167844</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>181543</t>
+          <t>202894</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>363396</t>
+          <t>387564</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>337472</t>
+          <t>357742</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>394706</t>
+          <t>416532</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>46,37%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>448409</t>
+          <t>479331</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>448409</t>
+          <t>479331</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>448409</t>
+          <t>479331</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>378444</t>
+          <t>418936</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>378444</t>
+          <t>418936</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>378444</t>
+          <t>418936</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>826854</t>
+          <t>898267</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>826854</t>
+          <t>898267</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>826854</t>
+          <t>898267</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>243607</t>
+          <t>269685</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>95780</t>
+          <t>247136</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>396762</t>
+          <t>292572</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>94639</t>
+          <t>105038</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>83613</t>
+          <t>93163</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104615</t>
+          <t>115780</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>338246</t>
+          <t>374723</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>137392</t>
+          <t>348450</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>491599</t>
+          <t>398358</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>60,92%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>421240</t>
+          <t>198598</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>268085</t>
+          <t>175711</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>569067</t>
+          <t>221147</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>70526</t>
+          <t>80567</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60550</t>
+          <t>69825</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81552</t>
+          <t>92442</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>491766</t>
+          <t>279165</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>338413</t>
+          <t>255530</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>692620</t>
+          <t>305438</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>46,71%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>664847</t>
+          <t>468283</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>664847</t>
+          <t>468283</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>664847</t>
+          <t>468283</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>165165</t>
+          <t>185605</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>165165</t>
+          <t>185605</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>165165</t>
+          <t>185605</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>830012</t>
+          <t>653888</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>830012</t>
+          <t>653888</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>830012</t>
+          <t>653888</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>609007</t>
+          <t>666734</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>569580</t>
+          <t>627467</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>644169</t>
+          <t>702551</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>638655</t>
+          <t>493626</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>539727</t>
+          <t>468333</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>799006</t>
+          <t>518549</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1247663</t>
+          <t>1160359</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1146312</t>
+          <t>1112577</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1514563</t>
+          <t>1202705</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>60,75%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>419540</t>
+          <t>458850</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>384378</t>
+          <t>423033</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>458967</t>
+          <t>498117</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>333864</t>
+          <t>360547</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>173513</t>
+          <t>335624</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>432792</t>
+          <t>385840</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>753403</t>
+          <t>819397</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>486503</t>
+          <t>777051</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>854754</t>
+          <t>867179</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>43,8%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1028547</t>
+          <t>1125584</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1028547</t>
+          <t>1125584</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1028547</t>
+          <t>1125584</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>972519</t>
+          <t>854173</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>972519</t>
+          <t>854173</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>972519</t>
+          <t>854173</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2001066</t>
+          <t>1979756</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2001066</t>
+          <t>1979756</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2001066</t>
+          <t>1979756</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>294645</t>
+          <t>361065</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>270178</t>
+          <t>335251</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>317655</t>
+          <t>386397</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>473543</t>
+          <t>538941</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>369150</t>
+          <t>516322</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>534260</t>
+          <t>561262</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>768188</t>
+          <t>900006</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>619199</t>
+          <t>865396</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>833502</t>
+          <t>933601</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>67,72%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>174092</t>
+          <t>198864</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>151082</t>
+          <t>173532</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>198559</t>
+          <t>224678</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>356805</t>
+          <t>279748</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>296088</t>
+          <t>257427</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>461198</t>
+          <t>302367</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>530897</t>
+          <t>478612</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>465583</t>
+          <t>445017</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>679886</t>
+          <t>513222</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>37,23%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>468737</t>
+          <t>559929</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>468737</t>
+          <t>559929</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>468737</t>
+          <t>559929</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>830348</t>
+          <t>818689</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>830348</t>
+          <t>818689</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>830348</t>
+          <t>818689</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1299085</t>
+          <t>1378618</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1299085</t>
+          <t>1378618</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1299085</t>
+          <t>1378618</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>84695</t>
+          <t>91298</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>61628</t>
+          <t>67921</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>108609</t>
+          <t>115098</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>446773</t>
+          <t>501275</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>420233</t>
+          <t>473143</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>472310</t>
+          <t>530456</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>531468</t>
+          <t>592573</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>494495</t>
+          <t>553214</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>567931</t>
+          <t>630183</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>58,82%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>153172</t>
+          <t>143224</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>129258</t>
+          <t>119424</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>176239</t>
+          <t>166601</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>307583</t>
+          <t>335596</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>282046</t>
+          <t>306415</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>334123</t>
+          <t>363728</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>460755</t>
+          <t>478820</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>424292</t>
+          <t>441210</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>497728</t>
+          <t>518179</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>48,37%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>237867</t>
+          <t>234522</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>237867</t>
+          <t>234522</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>237867</t>
+          <t>234522</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>754356</t>
+          <t>836871</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>754356</t>
+          <t>836871</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>754356</t>
+          <t>836871</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>992223</t>
+          <t>1071393</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>992223</t>
+          <t>1071393</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>992223</t>
+          <t>1071393</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1740590</t>
+          <t>1949166</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1292323</t>
+          <t>1876977</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1898230</t>
+          <t>2005709</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2067411</t>
+          <t>2096429</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1919948</t>
+          <t>2045847</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2320172</t>
+          <t>2151093</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3808001</t>
+          <t>4045595</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3414697</t>
+          <t>3965745</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4081664</t>
+          <t>4129626</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>58,86%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1609354</t>
+          <t>1465369</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1451714</t>
+          <t>1408826</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2057621</t>
+          <t>1537558</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1479510</t>
+          <t>1504873</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1226749</t>
+          <t>1450209</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1626973</t>
+          <t>1555455</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3088864</t>
+          <t>2970242</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2815201</t>
+          <t>2886211</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3482168</t>
+          <t>3050092</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>43,47%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3349944</t>
+          <t>3414535</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3349944</t>
+          <t>3414535</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3349944</t>
+          <t>3414535</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3546921</t>
+          <t>3601302</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3546921</t>
+          <t>3601302</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3546921</t>
+          <t>3601302</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6896865</t>
+          <t>7015837</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6896865</t>
+          <t>7015837</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6896865</t>
+          <t>7015837</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
